--- a/artfynd/S 1426-2025 artfynd.xlsx
+++ b/artfynd/S 1426-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97336636</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97336649</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97336659</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97336656</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97336634</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1350,6 +1380,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97336648</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1463,6 +1498,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97336654</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1576,6 +1616,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97336673</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1689,6 +1734,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97336653</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1802,6 +1852,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97336632</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1915,6 +1970,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97336637</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2028,6 +2088,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97336646</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2141,6 +2206,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97336650</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2254,6 +2324,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97336662</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2367,6 +2442,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97336665</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2480,6 +2560,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97336668</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2593,8 +2678,32 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97336678</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>